--- a/public/ezhliha_template_multi_sheet.xlsx
+++ b/public/ezhliha_template_multi_sheet.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -590,6 +590,20 @@
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>بعد التعبئة: افتح لوحة التحكم → «رفع البيانات» → اختر هذا الملف.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>• عمود «التصنيف الثانوي» اختياري (بدون نجمة): يُستخدم فقط إذا كان المزود يندرج تحت مستوى ثالث، مثال: التصنيف الفرعي = صوالين التجميل، التصنيف الثانوي = تصفيف الشعر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>• لا تضع التصنيف الثانوي داخل عمود التصنيف الفرعي — القوائم المنسدلة صارت منفصلة.</t>
         </is>
       </c>
     </row>
@@ -604,14 +618,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -657,105 +671,110 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>التصنيف الثانوي</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>الوصف</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>وصف السعر</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>السعر من</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>السعر إلى</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>تكفي من (شخص)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>تكفي إلى (شخص)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>رقم واتساب</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>رقم الاتصال</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>إنستقرام</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>تيك توك</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>تويتر (X)</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>سناب شات</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>العنوان</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>رابط الموقع (خرائط جوجل)</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>رابط اللوقو</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>روابط الصور</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>روابط الفيديوهات</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>التقييم (0-5)</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>مميز؟</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>الترتيب</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>نشط؟</t>
         </is>
@@ -782,7 +801,7 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>مطعم إيطالي أصيل يقدم أشهى المأكولات الإيطالية منذ عام 2002 
 مع قائمة متنوعة من الأطباق الإيطالية
@@ -790,61 +809,52 @@
 في موقع المناسبة لتجربة مميزة لضيوفكم</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>تبدأ الأسعار من 295 ريالًا للفرد
  بحد أدنى 20 شخصًا</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>295</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>20</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>9665010108560</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>aldenterest</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>aldenterest</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>جدة - السلامة</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/z1RZmjDCUCwTKopx8?g_st=ic</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>10</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -871,60 +881,49 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>الصحن الجميل تقدم بوفيهات للمناسبات بتشكيلة متنوعة من الأطباق
 مع إمكانية تخصيص المنيو حسب نوع المناسبة وعدد الضيوف
 مع التركيز على الجودة والتقديم الاحترافي</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>تبدأ من 160 ريال للفرد 
 بحد أدنى 30 شخص</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>160</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>30</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>9665523227190</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>belleplatecatering</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>24</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -951,63 +950,53 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>جرين سالاد تقدم بوفيهات منزلية مع خدمة تنسيق طاولات البوفيه
  والسخانات، وتوفر مستلزمات التقديم كاملة، بما في ذلك الصحون
  والملاعق والشوك، مع تنسيقات أنيقة تناسب مختلف المناسبات</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>تبدأ من 2500 ريال ل 15 شخص</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2500</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>15</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>9665305309910</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>_greensalad1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>greensalad.18</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>21</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1034,62 +1023,51 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>ريد ون كيترنغ تقدم خدمات الضيافة والبوفيهات الراقية للمناسبات
 مع تشكيلة متنوعة من الأصناف وخدمة احترافية تناسب 
 مختلف الاحتفالات والتجمعات</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>تبدأ من 300 ربال للشخص 
 بحد أدنى 20 شخص</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>20</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>9665306073730</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>red1_catering</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>red1.catering</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>20</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1116,64 +1094,54 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>سيلفرسبون تقدم خدمات البوفيهات والضيافة للمناسبات الخاصة
  وفعاليات الشركات، مع بوفيهات شرقية وغربية، بخبرة منذ عام 2014
 وتوفر تجربة ضيافة احترافية تناسب مختلف المناسبات</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>تبدأ من 200 ريال للشخص 
 بحد أدنى 25 شخص</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>200</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>25</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>9665309022880</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>silverspoonksa</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>جدة - طريق المدينة</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/dpasfBgzgzNWKzDQA?g_st=ic</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>29</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1200,60 +1168,50 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>تاج كيترنغ يقدم خدمات البوفيهات والضيافة للمناسبات الخاصة 
 مع خيارات متنوعة تناسب مختلف المناسبات وتُقدَّم بأسلوب احترافي</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>تبدأ من 1900 ريال ل  10- 15 شخص</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1900</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>15</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>9665435320650</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>taj.c.m</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>23</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1280,70 +1238,62 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>حلويات الجونة تقدم تشكيلة متنوعة من الحلويات الشرقية والغربية
 مع خدمات بوفيهات وضيافة للمناسبات، بخبرة تمتد لأكثر من 20 عامًا
 ولها عدة فروع</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>باقات البوفيه تبدأ من 2,587 ريال لـ 15 شخص
 سعر البوفيه بالمتر يبدأ من 575 ريال</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>575</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2587</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>15</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>9665410010070</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>aljonah_sweets</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>aljonah_sweets</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>جدة - الصفا</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/HaQmr5KLUScYJW9HA?g_st=ic</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>16</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1370,64 +1320,54 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>مجموعة فنادق الدار البيضاء تقدم خدمات البوفيهات والضيافة الخارجية
  للمناسبات، مع بوفيهات ووجبات جاهزة، وقوائم طعام شرقية وعالمية
 بإشراف طهاة محترفين وفريق ضيافة مدرب لتقديم خدمة فندقية عالية الجودة</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>تبدأ الأسعار من 300 ريال للشخص 
 بحد أدنى 20 شخص ، غير شاملة الضريبة</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>300</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>20</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>9661222222030</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>cgrouphotels</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>جدة - طريق المدينة</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/45VUVUMTq9x3vgC2A?g_st=ic</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>14</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1454,68 +1394,59 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>شركة الشرافة تقدم خدمات الضيافة والبوفيهات للمناسبات بخبرة
  تتجاوز 25 عامًا، مع تشكيلة متنوعة من المأكولات العالمية
 وخدمة احترافية تناسب مختلف المناسبات</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>تبدأ من 370 ريال للفرد 
 بحد أدنى 30 شخص</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>370</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>30</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>9665838823330</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>alshurafarest</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>alshurafarest</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>جدة - الحمراء</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/1KTMJLz8e35Rxk7j8?g_st=ic</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>22</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1542,7 +1473,7 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>الطهاة الخمس تقدم خدمات الضيافة والبوفيهات الراقية بخبرة
  تتجاوز 25 عامًا، مع تشكيلة متنوعة من الأصناف، وخدمة الطبخ الحي
@@ -1550,7 +1481,7 @@
  مختلف المناسبات بأسلوب احترافي</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>يبدأ من 160 ربال للفرد 
 بحد أدنى 30 شخص 
@@ -1558,53 +1489,44 @@
 بحد أدنى 30 شخص</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>100</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>30</v>
       </c>
       <c r="J11" t="n">
         <v>30</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>30</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>9665700220220</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>5chefs.sa</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>5chefsa</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>28</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1631,65 +1553,56 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>يقدم بوفيه المذاق الفاخر خدمة تنسيق وتجهيز البوفيهات باحترافية
 مع تشكيلة متنوعة من الأطباق تجمع بين جودة المذاق وأناقة التقديم
  لتناسب مختلف المناسبات والجمعات</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>تبدأ الأسعار من 600 ريال لـ 10–15 شخصًا</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>600</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>10</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>15</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>9665662342610</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>almathaq_al</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>mathaqmm</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>8</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1716,69 +1629,60 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>مطعم بريوشيه يقدم تشكيلة متنوعة من الأطباق اللذيذة
  بجودة عالية، مع إمكانية طلب بوفيه للمناسبات أو طلب أطباق منفصلة 
 حسب احتياجكم وعدد الأشخاص</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>تبدأ أسعار البوفيه من 1,590 ريالًا لـ 10 أشخاص
 تبدأ أسعار الأطباق المنفصلة 
 من 125 ريالًا للطبق، ويكفي 8–12 شخصًا</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>1590</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>10</v>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>9665323169190</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>brioche_sa</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>brioche_sa</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>جدة - السلامة</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/D9VHjHnHpQvkYoWj9?g_st=ic</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>3</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1805,62 +1709,52 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>بوفيهات رنوش توفر خيارات متنوعة من الأطباق العربية والعالمية
 مع تنسيق وتجهيز البوفيهات بما يناسب مختلف المناسبات والاحتفالات</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>تبدأ الباقات من 3160 ريال ل 20 شخص</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>3160</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>20</v>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>966593273137</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>rnoshcatering</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>ranosh_858</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>2</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1887,63 +1781,53 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>توفيدو تقدم خدمات الضيافة والبوفيهات للمناسبات، مع تشكيلة متنوعة
  من الأصناف، وخدمة الطبخ الحي، لتقديم تجربة ضيافة احترافية
  تناسب مختلف المناسبات</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>باقات البوفيه تبدأ من 2600 ريال ل 20 شخص</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>2600</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>20</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>9665498345550</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>tofedo</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>tofedo1</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>15</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -1970,68 +1854,59 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>مطعم دندن متخصص في المأكولات الإندونيسية
 ويقدم تشكيلة متنوعة من الأطباق الإندونيسية الأصيلة، مع خدمة البوفيهات 
 وخيارات تناسب مختلف المناسبات ، ولهم عدة فروع في مدينة جدة</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>تبدأ من 126,5 ريال للشخص الواحد 
 بحد أدنى 15 شخص</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>126.5</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>15</v>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>9665540700660</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>dendenksa</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>dendenksa</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>جدة - النهضة</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/nJC3rZ2mjRDZVMHz6?g_st=ic</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>12</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2058,7 +1933,7 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>رنا إدريس – عزيمتك من طبخ البيت
 تقدم أطباقًا منزلية بطعم أصيل، مع تشكيلة متنوعة من السلطات، 
@@ -2066,55 +1941,45 @@
 ولا تقدم خدمة البوفيه</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>تبدأ الأسعار من 150 ريال للطبق
 ويكفي 8–10 أشخاص</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>150</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>10</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>9665656950600</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>rana_food</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>جدة - النابغة الذبياني</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>5</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2141,62 +2006,52 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>الفخامة تقدم بوفيهات للمناسبات بتشكيلة متنوعة من الأطباق المحضّرة
  بمكونات مختارة بعناية وجودة عالية  لتناسب مختلف المناسبات والتجمعات</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>تبدأ من 1000 ريال ل 10 أشخاص</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1000</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>9665581453440</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>rosealfakhama</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>rosealfakhama</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>25</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2223,63 +2078,53 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>ريلاشز إيفنتس متخصصة في تنظيم وتنفيذ المناسبات الفاخرة
 وتقدم خدمات تموين وضيافة متكاملة تشمل البوفيهات
 مع اهتمام بأدق التفاصيل لتقديم تجربة راقية تليق بضيوفكم</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>تبدأ من 2,950 ريال ل 20 شخص</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>2950</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>20</v>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>9665677315840</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>relusious.events</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>reluscious</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>9</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2306,68 +2151,59 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>مطعم زايكاكي متخصص في المأكولات الهندية
 ويقدم تشكيلة متنوعة من الأطباق الهندية الأصيلة، مع خيارات تناسب 
 مختلف المناسبات وخدمة البوفيهات</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>تبدأ من 295 ريال للفرد 
 بحد أدنى 20 شخص</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>295</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>20</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>9665363337460</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>zaikaki.ksa</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>zaikaki.ksa</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>جدة - طريق الملك عبدالعزيز</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/9yuS968wabZKDb9MA?g_st=ic</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>13</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2394,14 +2230,14 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>تقدم زي كيتشن أطباقًا منزلية شهية
 مع إمكانية طلب أطباق منفصلة أو خدمة بوفيه للمناسبات
 حسب عدد الأشخاص واحتياجكم</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>خدمة البوفيه تبدأ من 250 ريالًا للشخص
 بحد أدنى 20 شخصًا
@@ -2409,53 +2245,44 @@
 وتختلف حسب الحجم</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>80</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>250</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>20</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>9665556565850</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>zkitchen_ksa</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>zkitchen_ksa</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>4</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2482,58 +2309,46 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>عائلة السفرة السعودية تقدم تشكيلة واسعة من الأطباق من المطبخ السعودي
  والمطبخ العالمي، مع خيارات تناسب مختلف المناسبات. تتوفر خدمة البوفيهات
 بالإضافة إلى إمكانية طلب أطباق منفصلة بأحجام متنوعة حسب الاحتياج</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>تبدأ أسعار الأطباق من 150 ريال
 وتختلف حسب الحجم</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>150</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>9665563364440</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>saudisofra</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>6</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2560,61 +2375,50 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>بيغ ديش تقدم خدمات الضيافة والبوفيهات للمناسبات، مع تشكيلة متنوعة 
 من الأطعمة وخدمات متكاملة لتنظيم الضيافة، بإشراف فريق متخصص 
 لضمان تجربة مميزة تناسب مختلف المناسبات</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>تبدأ من 180 ريال للشهص شامل الخدمات</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>180</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>9665411584060</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>bigdish_jeddah_catering</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>big_dish_catering</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>27</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2641,63 +2445,52 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>تقدم  أشهى الأطباق المنزلية للمناسبات والجمعات
 مع تشكيلة متنوعة من المقبلات، الباستا، والسلطات
 تتوفر إمكانية طلب أطباق منفردة أو باقات متكاملة حسب عدد الأشخاص</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>تبدأ الاسعار من 2100</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>966503000120</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>966503000120</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>lamyaalesayi</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>https://safulzxbedldleulbdsj.supabase.co/storage/v1/object/public/provider-images/a04e49da-0589-4291-acb5-fec4a74d3101/logo_url-1783695313968.jpg</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>1</v>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2724,65 +2517,56 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>يقدم لودي بوفيه تشكيلة متنوعة من الأطباق الرئيسية، المقبلات، والحلويات، 
 مع خيارات تناسب مختلف المناسبات والجمعات</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>تبدأ أسعار الباقات من 2,500 ريال
  لـ 15–20 شخص</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>2500</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>15</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>20</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>9665569769780</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>loodybuffet.sa</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>loody_flavour</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>7</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2809,57 +2593,45 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>ليندا ليشيز تقدم بوفيهات منزلية وطلبات فردية، مع تشكيلة متنوعة
  من الأطباق المناسبة للمناسبات والجمعات</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>تبدأ أسعار الأطباق من 150 ريالًا
 وتختلف حسب الحجم</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>150</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>966555657080</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Lindalicious.catering.sa</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>19</v>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2886,7 +2658,7 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>ميدرينيوس للضيافة تقدم خدمات البوفيهات والضيافة للمناسبات
 مع تشكيلة من الأصناف العالمية، وفينجر فود، ومحطات الطبخ المباشر
@@ -2894,7 +2666,7 @@
 مع توفير فريق ضيافة عند الطلب</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>البوفيه يبدأ من 260 ريالًا للشخص
  (بحد أدنى 20 شخصًا)
@@ -2902,59 +2674,52 @@
 وتكفي 10–15 شخصًا</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>70</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>260</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>15</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>9665084473330</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>medrainus</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>medrainus6</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>جدة - الروضة</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/xvrSpjb2xMUg4X1m9?g_st=ic</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>18</v>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -2981,7 +2746,7 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>مها بيكري مخبز متخصص في المخبوزات السعودية، ويقدم تشكيلة
  متنوعة من المخبوزات الطازجة، مع إمكانية طلب البوفيه
@@ -2989,60 +2754,51 @@
 ويُعد الشريك المحشي بحشواته المتنوعة من أشهر منتجاته</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>تبدأ أسعار البوفيه من 2,500 ريال لـ 20 شخص</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>2500</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>20</v>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>9665445464200</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>maha.bakery</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>maha..bakery</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>جدة - الشاطئ</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/E2WwzFUjA1hUGn9KA?g_st=ic</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>11</v>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -3069,7 +2825,7 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>موزايك تقدم خدمات الضيافة والبوفيهات للمناسبات الخاصة
  وفعاليات الشركات مع قوائم طعام متنوعة، وكوفي كورنر، وفينجر فود
@@ -3077,56 +2833,46 @@
 لتقديم تجربة ضيافة متكاملة وأنيقة تناسب مختلف المناسبات</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>تبدأ من 180 ريال للفرد ، بحد أدنى 25 شخص</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>180</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>25</v>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>9665569177990</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>mozaiccateringsa</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>mozaiccateringsa</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>جدة | توصيل للموقع</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>26</v>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
@@ -3153,14 +2899,14 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>مخابز وحلويات نعمة تقدم تشكيلة متنوعة من المخبوزات الطازجة
 ، والحلويات، والكيك، والمعجنات، والموالح، بالإضافة إلى
  خدمات البوفيهات والضيافة للمناسبات، ولها عدة فروع في مدينة جدة</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>تبدأ باقات البوفيه من 1,700 ريال،ل 10–15 شخص
 سعر البوفيه بالمتر: 500 ريال للمتر
@@ -3168,66 +2914,59 @@
 الحد الأدنى للطلب: 10 أمتار</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>500</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>1700</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>9669200006790</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>neamahbakery</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>neamahbakery</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>جدة - الروضة</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/nfCLzxUCW5SWXt5r7?g_st=ic</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>17</v>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"الرياض,جدة,مكة المكرمة,المدينة المنورة,الدمام,الخبر"</formula1>
     </dataValidation>
@@ -3235,12 +2974,15 @@
       <formula1>"القاعات والاستراحات,تنسيق وتصميم الحفلات,تفاصيل الضيافة,الدعوات الالكترونية,التصوير والتوثيق,إطلالة المناسبة,السبا والخدمات المنزلية,خدمات إضافية"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=_قوائم!$A$2:$A$18</formula1>
+      <formula1>=_قوائم!$A$2:$A$16</formula1>
     </dataValidation>
-    <dataValidation sqref="W2:W1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=_قوائم!$D$2:$D$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="X2:X1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"نعم,لا"</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Z2:Z1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"نعم,لا"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3254,7 +2996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3263,14 +3005,9 @@
           <t>التصنيفات الفرعية</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>المدن</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>التصنيفات</t>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>التصنيفات الثانوية</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3017,9 @@
           <t>ارسال الدعوات</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>الرياض</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>القاعات والاستراحات</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>تصفيف الشعر  💇🏻‍♀️</t>
         </is>
       </c>
     </row>
@@ -3297,14 +3029,9 @@
           <t>البوفيهات</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>جدة</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>تنسيق وتصميم الحفلات</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>خبيرات التجميل (مكياج)💄</t>
         </is>
       </c>
     </row>
@@ -3314,16 +3041,6 @@
           <t>الصبابات و المباشرات</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>مكة المكرمة</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>تفاصيل الضيافة</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3331,138 +3048,86 @@
           <t>الضيافة</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>المدينة المنورة</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>الدعوات الالكترونية</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>تصفيف الشعر  💇🏻‍♀️</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>الدمام</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>التصوير والتوثيق</t>
+          <t>تصميم الدعوات</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>تصميم الدعوات</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>الخبر</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>إطلالة المناسبة</t>
+          <t>تصوير الجوال</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>تصوير الجوال</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>السبا والخدمات المنزلية</t>
+          <t>تصوير الكاميرا الاحترافي</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>تصوير الكاميرا الاحترافي</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>خدمات إضافية</t>
+          <t>ركن القهوة والحلويات</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>خبيرات التجميل (مكياج)💄</t>
+          <t>ركن تصوير (فوتوبوث)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ركن القهوة والحلويات</t>
+          <t>شاليهات واستراحات</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ركن تصوير (فوتوبوث)</t>
+          <t>صوالين التجميل</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>شاليهات واستراحات</t>
+          <t>قاعات فندقية</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>صوالين التجميل</t>
+          <t>قصور أفراح</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>قاعات فندقية</t>
+          <t>مداخل العطور</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>قصور أفراح</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>مداخل العطور</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
           <t>وصيفة العروسة</t>
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3557,8 +3222,6 @@
           <t>تبدأ من 2100</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -3665,7 +3328,6 @@
           <t>https://safulzxbedldleulbdsj.supabase.co/storage/v1/object/public/provider-images/a04e49da-0589-4291-acb5-fec4a74d3101/service-1783694089166.png</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -3756,7 +3418,6 @@
           <t>شارع البساتين</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>0544135349</t>
@@ -3787,7 +3448,6 @@
           <t>طريق الامير سلطان</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>0573444242</t>
